--- a/docs/launch_checklist.xlsx
+++ b/docs/launch_checklist.xlsx
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -768,6 +768,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2237,6 +2238,33 @@
       <c r="F49" s="8" t="inlineStr">
         <is>
           <t>Triggered by docs/reminders.xlsx Jul 6 deadline. Optional — can defer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Build Stripe pause/resume orchestration for account-deletion grace period</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>When a coach with an active Stripe subscription clicks 'Delete my account', the 30-day grace period should PAUSE Stripe billing (no renewals charged during grace). On reactivation, if a billing cycle elapsed during grace, charge the user once for the missed cycle then resume on the original cadence. On grace expiry (no reactivation), cancel the Stripe subscription cleanly. Without this, paying coaches who request deletion either keep getting charged during their grace (bad) or get free coverage on reactivation (also bad). Requires: edge function for pause/resume Stripe API calls + webhook handler updates to write billing:* events into the activity_events table. DB lifecycle (profiles.scheduled_for_deletion_at + RPCs + cron) is already live.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>M+C</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
